--- a/figs/data/fig7_mixX_v6.xlsx
+++ b/figs/data/fig7_mixX_v6.xlsx
@@ -205,9 +205,6 @@
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
               <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
-              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
